--- a/data/TKF.MI.xlsx
+++ b/data/TKF.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11571741104126</t>
+    <t xml:space="preserve">4.11571788787842</t>
   </si>
   <si>
     <t xml:space="preserve">TKF.MI</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">4.09679508209229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17721700668335</t>
+    <t xml:space="preserve">4.17721748352051</t>
   </si>
   <si>
     <t xml:space="preserve">4.25763893127441</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">4.36644554138184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35698461532593</t>
+    <t xml:space="preserve">4.35698413848877</t>
   </si>
   <si>
     <t xml:space="preserve">4.40902185440063</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">4.35225343704224</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29075384140015</t>
+    <t xml:space="preserve">4.2907543182373</t>
   </si>
   <si>
     <t xml:space="preserve">4.24344730377197</t>
@@ -95,34 +95,34 @@
     <t xml:space="preserve">4.02583456039429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04002666473389</t>
+    <t xml:space="preserve">4.04002618789673</t>
   </si>
   <si>
     <t xml:space="preserve">4.05894947052002</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92175889015198</t>
+    <t xml:space="preserve">3.9217586517334</t>
   </si>
   <si>
     <t xml:space="preserve">4.11098718643188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95960426330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92648959159851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94541239738464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04475784301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95487380027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93595099449158</t>
+    <t xml:space="preserve">3.95960474014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92648983001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94541263580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04475736618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95487356185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.935950756073</t>
   </si>
   <si>
     <t xml:space="preserve">4.03056526184082</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">3.96906614303589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97379660606384</t>
+    <t xml:space="preserve">3.97379636764526</t>
   </si>
   <si>
     <t xml:space="preserve">3.85079836845398</t>
@@ -149,10 +149,10 @@
     <t xml:space="preserve">3.59533977508545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72779989242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81295275688171</t>
+    <t xml:space="preserve">3.72779965400696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81295251846313</t>
   </si>
   <si>
     <t xml:space="preserve">3.99271941184998</t>
@@ -161,13 +161,13 @@
     <t xml:space="preserve">4.00691175460815</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01164197921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8791823387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76564526557922</t>
+    <t xml:space="preserve">4.01164245605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87918257713318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7656455039978</t>
   </si>
   <si>
     <t xml:space="preserve">3.78456830978394</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">3.82714462280273</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53857135772705</t>
+    <t xml:space="preserve">3.53857111930847</t>
   </si>
   <si>
     <t xml:space="preserve">3.57641696929932</t>
@@ -191,10 +191,10 @@
     <t xml:space="preserve">3.37299633026123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23107528686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13646078109741</t>
+    <t xml:space="preserve">3.23107504844666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13646101951599</t>
   </si>
   <si>
     <t xml:space="preserve">3.50072574615479</t>
@@ -221,10 +221,10 @@
     <t xml:space="preserve">4.37117624282837</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30967664718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43740653991699</t>
+    <t xml:space="preserve">4.30967712402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43740606307983</t>
   </si>
   <si>
     <t xml:space="preserve">4.37590742111206</t>
@@ -236,13 +236,13 @@
     <t xml:space="preserve">4.52255916595459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61717367172241</t>
+    <t xml:space="preserve">4.61717319488525</t>
   </si>
   <si>
     <t xml:space="preserve">4.68340301513672</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92940044403076</t>
+    <t xml:space="preserve">4.9293999671936</t>
   </si>
   <si>
     <t xml:space="preserve">5.27240037918091</t>

--- a/data/TKF.MI.xlsx
+++ b/data/TKF.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11571788787842</t>
+    <t xml:space="preserve">4.11571741104126</t>
   </si>
   <si>
     <t xml:space="preserve">TKF.MI</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">4.09679508209229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17721748352051</t>
+    <t xml:space="preserve">4.17721700668335</t>
   </si>
   <si>
     <t xml:space="preserve">4.25763893127441</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">4.36644554138184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35698413848877</t>
+    <t xml:space="preserve">4.35698461532593</t>
   </si>
   <si>
     <t xml:space="preserve">4.40902185440063</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">4.35225343704224</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2907543182373</t>
+    <t xml:space="preserve">4.29075384140015</t>
   </si>
   <si>
     <t xml:space="preserve">4.24344730377197</t>
@@ -95,34 +95,34 @@
     <t xml:space="preserve">4.02583456039429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04002618789673</t>
+    <t xml:space="preserve">4.04002666473389</t>
   </si>
   <si>
     <t xml:space="preserve">4.05894947052002</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9217586517334</t>
+    <t xml:space="preserve">3.92175889015198</t>
   </si>
   <si>
     <t xml:space="preserve">4.11098718643188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95960474014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92648983001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94541263580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04475736618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95487356185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.935950756073</t>
+    <t xml:space="preserve">3.95960426330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92648959159851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94541239738464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04475784301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95487380027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93595099449158</t>
   </si>
   <si>
     <t xml:space="preserve">4.03056526184082</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">3.96906614303589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97379636764526</t>
+    <t xml:space="preserve">3.97379660606384</t>
   </si>
   <si>
     <t xml:space="preserve">3.85079836845398</t>
@@ -149,10 +149,10 @@
     <t xml:space="preserve">3.59533977508545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72779965400696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81295251846313</t>
+    <t xml:space="preserve">3.72779989242554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81295275688171</t>
   </si>
   <si>
     <t xml:space="preserve">3.99271941184998</t>
@@ -161,13 +161,13 @@
     <t xml:space="preserve">4.00691175460815</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01164245605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87918257713318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7656455039978</t>
+    <t xml:space="preserve">4.01164197921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8791823387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76564526557922</t>
   </si>
   <si>
     <t xml:space="preserve">3.78456830978394</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">3.82714462280273</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53857111930847</t>
+    <t xml:space="preserve">3.53857135772705</t>
   </si>
   <si>
     <t xml:space="preserve">3.57641696929932</t>
@@ -191,10 +191,10 @@
     <t xml:space="preserve">3.37299633026123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23107504844666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13646101951599</t>
+    <t xml:space="preserve">3.23107528686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13646078109741</t>
   </si>
   <si>
     <t xml:space="preserve">3.50072574615479</t>
@@ -221,10 +221,10 @@
     <t xml:space="preserve">4.37117624282837</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30967712402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43740606307983</t>
+    <t xml:space="preserve">4.30967664718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43740653991699</t>
   </si>
   <si>
     <t xml:space="preserve">4.37590742111206</t>
@@ -236,13 +236,13 @@
     <t xml:space="preserve">4.52255916595459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61717319488525</t>
+    <t xml:space="preserve">4.61717367172241</t>
   </si>
   <si>
     <t xml:space="preserve">4.68340301513672</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9293999671936</t>
+    <t xml:space="preserve">4.92940044403076</t>
   </si>
   <si>
     <t xml:space="preserve">5.27240037918091</t>
